--- a/artfynd/A 10698-2022 artfynd.xlsx
+++ b/artfynd/A 10698-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136537639</v>
       </c>
       <c r="B2" t="n">
-        <v>108105</v>
+        <v>108108</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136537774</v>
       </c>
       <c r="B3" t="n">
-        <v>108105</v>
+        <v>108108</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136537803</v>
       </c>
       <c r="B4" t="n">
-        <v>108105</v>
+        <v>108108</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 10698-2022 artfynd.xlsx
+++ b/artfynd/A 10698-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136537639</v>
       </c>
       <c r="B2" t="n">
-        <v>108108</v>
+        <v>108109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136537774</v>
       </c>
       <c r="B3" t="n">
-        <v>108108</v>
+        <v>108109</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136537803</v>
       </c>
       <c r="B4" t="n">
-        <v>108108</v>
+        <v>108109</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 10698-2022 artfynd.xlsx
+++ b/artfynd/A 10698-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136537639</v>
       </c>
       <c r="B2" t="n">
-        <v>108109</v>
+        <v>108114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136537774</v>
       </c>
       <c r="B3" t="n">
-        <v>108109</v>
+        <v>108114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136537803</v>
       </c>
       <c r="B4" t="n">
-        <v>108109</v>
+        <v>108114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 10698-2022 artfynd.xlsx
+++ b/artfynd/A 10698-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136537639</v>
       </c>
       <c r="B2" t="n">
-        <v>108114</v>
+        <v>108116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136537774</v>
       </c>
       <c r="B3" t="n">
-        <v>108114</v>
+        <v>108116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136537803</v>
       </c>
       <c r="B4" t="n">
-        <v>108114</v>
+        <v>108116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 10698-2022 artfynd.xlsx
+++ b/artfynd/A 10698-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136537639</v>
       </c>
       <c r="B2" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136537774</v>
       </c>
       <c r="B3" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136537803</v>
       </c>
       <c r="B4" t="n">
-        <v>108116</v>
+        <v>108122</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 10698-2022 artfynd.xlsx
+++ b/artfynd/A 10698-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136537639</v>
       </c>
       <c r="B2" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136537774</v>
       </c>
       <c r="B3" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136537803</v>
       </c>
       <c r="B4" t="n">
-        <v>108122</v>
+        <v>108124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 10698-2022 artfynd.xlsx
+++ b/artfynd/A 10698-2022 artfynd.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Väg och Miljö AB, Elvira Klang</t>
+          <t>Elvira Klang, Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 10698-2022 artfynd.xlsx
+++ b/artfynd/A 10698-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136537639</v>
       </c>
       <c r="B2" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136537774</v>
       </c>
       <c r="B3" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136537803</v>
       </c>
       <c r="B4" t="n">
-        <v>108124</v>
+        <v>108125</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 10698-2022 artfynd.xlsx
+++ b/artfynd/A 10698-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136537639</v>
       </c>
       <c r="B2" t="n">
-        <v>108125</v>
+        <v>108131</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elvira Klang, Väg och Miljö AB</t>
+          <t>Väg och Miljö AB, Elvira Klang</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -789,7 +789,7 @@
         <v>136537774</v>
       </c>
       <c r="B3" t="n">
-        <v>108125</v>
+        <v>108131</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136537803</v>
       </c>
       <c r="B4" t="n">
-        <v>108125</v>
+        <v>108131</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 10698-2022 artfynd.xlsx
+++ b/artfynd/A 10698-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136537639</v>
       </c>
       <c r="B2" t="n">
-        <v>108131</v>
+        <v>108135</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136537774</v>
       </c>
       <c r="B3" t="n">
-        <v>108131</v>
+        <v>108135</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136537803</v>
       </c>
       <c r="B4" t="n">
-        <v>108131</v>
+        <v>108135</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 10698-2022 artfynd.xlsx
+++ b/artfynd/A 10698-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136537639</v>
       </c>
       <c r="B2" t="n">
-        <v>108135</v>
+        <v>108137</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136537774</v>
       </c>
       <c r="B3" t="n">
-        <v>108135</v>
+        <v>108137</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136537803</v>
       </c>
       <c r="B4" t="n">
-        <v>108135</v>
+        <v>108137</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 10698-2022 artfynd.xlsx
+++ b/artfynd/A 10698-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136537639</v>
       </c>
       <c r="B2" t="n">
-        <v>108137</v>
+        <v>108139</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136537774</v>
       </c>
       <c r="B3" t="n">
-        <v>108137</v>
+        <v>108139</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136537803</v>
       </c>
       <c r="B4" t="n">
-        <v>108137</v>
+        <v>108139</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 10698-2022 artfynd.xlsx
+++ b/artfynd/A 10698-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136537639</v>
       </c>
       <c r="B2" t="n">
-        <v>108139</v>
+        <v>108152</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136537774</v>
       </c>
       <c r="B3" t="n">
-        <v>108139</v>
+        <v>108152</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136537803</v>
       </c>
       <c r="B4" t="n">
-        <v>108139</v>
+        <v>108152</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 10698-2022 artfynd.xlsx
+++ b/artfynd/A 10698-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136537639</v>
       </c>
       <c r="B2" t="n">
-        <v>108152</v>
+        <v>108154</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136537774</v>
       </c>
       <c r="B3" t="n">
-        <v>108152</v>
+        <v>108154</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136537803</v>
       </c>
       <c r="B4" t="n">
-        <v>108152</v>
+        <v>108154</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
